--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8BB2E2-7078-4EC7-8A90-7A66C214169A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97DD4B9-9FEC-4BD9-BF28-8D968643B81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>Too much</t>
+  </si>
+  <si>
+    <t>too much</t>
   </si>
 </sst>
 </file>
@@ -1088,26 +1091,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B8" s="14">
+        <v>420</v>
+      </c>
+      <c r="C8" s="14">
+        <v>50</v>
+      </c>
+      <c r="D8" s="14">
+        <v>100</v>
+      </c>
+      <c r="E8" s="14">
+        <v>50</v>
+      </c>
+      <c r="F8" s="14">
+        <v>100</v>
+      </c>
+      <c r="G8" s="14">
+        <v>2</v>
+      </c>
+      <c r="H8" s="14">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97DD4B9-9FEC-4BD9-BF28-8D968643B81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3BA82A-EB9C-47AC-84B0-35ECC3690C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -220,6 +220,12 @@
   </si>
   <si>
     <t>too much</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>goog</t>
   </si>
 </sst>
 </file>
@@ -1137,26 +1143,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B9" s="14">
+        <v>420</v>
+      </c>
+      <c r="C9" s="14">
+        <v>40</v>
+      </c>
+      <c r="D9" s="14">
+        <v>30</v>
+      </c>
+      <c r="E9" s="14">
+        <v>20</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>510</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>930</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C3BA82A-EB9C-47AC-84B0-35ECC3690C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B52B033-C41F-4916-9A3D-ACBEA4EC644B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -225,7 +225,13 @@
     <t>Low</t>
   </si>
   <si>
-    <t>goog</t>
+    <t>good</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1189,26 +1195,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B10" s="14">
+        <v>620</v>
+      </c>
+      <c r="C10" s="14">
+        <v>10</v>
+      </c>
+      <c r="D10" s="14">
+        <v>300</v>
+      </c>
+      <c r="E10" s="14">
+        <v>250</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>90</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B52B033-C41F-4916-9A3D-ACBEA4EC644B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E497B991-0B72-41B9-8381-537BD68E122B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>too good</t>
   </si>
 </sst>
 </file>
@@ -1241,26 +1247,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B11" s="14">
+        <v>420</v>
+      </c>
+      <c r="C11" s="14">
+        <v>15</v>
+      </c>
+      <c r="D11" s="14">
+        <v>350</v>
+      </c>
+      <c r="E11" s="14">
+        <v>100</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>5</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E497B991-0B72-41B9-8381-537BD68E122B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF943809-CBEA-42FE-81A5-5BC7CD011392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>too good</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>too bad</t>
   </si>
 </sst>
 </file>
@@ -1293,26 +1299,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B12" s="14">
+        <v>360</v>
+      </c>
+      <c r="C12" s="14">
+        <v>20</v>
+      </c>
+      <c r="D12" s="14">
+        <v>100</v>
+      </c>
+      <c r="E12" s="14">
+        <v>150</v>
+      </c>
+      <c r="F12" s="14">
+        <v>200</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF943809-CBEA-42FE-81A5-5BC7CD011392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797A425A-8BFF-4D53-A03B-89046723E579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1345,26 +1345,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B13" s="14">
+        <v>420</v>
+      </c>
+      <c r="C13" s="14">
+        <v>15</v>
+      </c>
+      <c r="D13" s="14">
+        <v>60</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>595</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{797A425A-8BFF-4D53-A03B-89046723E579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB26500-0CAB-4672-B3BC-4D1D1BED7CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1391,26 +1391,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B14" s="14">
+        <v>520</v>
+      </c>
+      <c r="C14" s="14">
+        <v>10</v>
+      </c>
+      <c r="D14" s="14">
+        <v>90</v>
+      </c>
+      <c r="E14" s="14">
+        <v>100</v>
+      </c>
+      <c r="F14" s="14">
+        <v>250</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>10</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB26500-0CAB-4672-B3BC-4D1D1BED7CA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE157E29-3E74-467B-B22D-967F16D839A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1437,26 +1437,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B15" s="14">
+        <v>620</v>
+      </c>
+      <c r="C15" s="14">
+        <v>10</v>
+      </c>
+      <c r="D15" s="14">
+        <v>250</v>
+      </c>
+      <c r="E15" s="14">
+        <v>250</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>15</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>295</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE157E29-3E74-467B-B22D-967F16D839A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F073E4C4-CA9B-4BC6-B0F0-4411F7D81E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1483,26 +1483,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B16" s="14">
+        <v>720</v>
+      </c>
+      <c r="C16" s="14">
+        <v>10</v>
+      </c>
+      <c r="D16" s="14">
+        <v>200</v>
+      </c>
+      <c r="E16" s="14">
+        <v>60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/1234567 (1).xlsx
+++ b/1234567 (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Desktop\python\776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F073E4C4-CA9B-4BC6-B0F0-4411F7D81E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755ABFBA-2FF4-4162-A18C-641CC963306E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -225,9 +225,6 @@
     <t>Low</t>
   </si>
   <si>
-    <t>good</t>
-  </si>
-  <si>
     <t>Very Satisfied</t>
   </si>
   <si>
@@ -237,13 +234,10 @@
     <t>Excellent</t>
   </si>
   <si>
-    <t>too good</t>
-  </si>
-  <si>
     <t>Very Unsatisfied</t>
   </si>
   <si>
-    <t>too bad</t>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -1203,7 +1197,7 @@
         <v>61</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1243,13 +1237,13 @@
         <v>49</v>
       </c>
       <c r="L10" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M10" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>64</v>
-      </c>
       <c r="N10" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1286,13 +1280,13 @@
         <v>300</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N11" s="17" t="s">
         <v>66</v>
@@ -1335,13 +1329,13 @@
         <v>57</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>61</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -1387,7 +1381,7 @@
         <v>61</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1433,7 +1427,7 @@
         <v>51</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1479,7 +1473,7 @@
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1525,30 +1519,54 @@
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B17" s="14">
+        <v>620</v>
+      </c>
+      <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
+        <v>50</v>
+      </c>
+      <c r="E17" s="14">
+        <v>30</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>200</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>
